--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TEKNEI BIZKAIA ZORNOTZA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TEKNEI BIZKAIA ZORNOTZA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,73 +565,73 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>10.777</v>
+        <v>10.7854</v>
       </c>
       <c r="E2" t="n">
-        <v>6.563800000000001</v>
+        <v>7.0353</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2132</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0173</v>
+        <v>7.0817</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8304</v>
+        <v>2.8931</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1869</v>
+        <v>4.188499999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7717</v>
+        <v>6.0748</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1245</v>
+        <v>3.3023</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6472</v>
+        <v>2.7725</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2456</v>
+        <v>1.0069</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2941</v>
+        <v>-0.4091</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5396</v>
+        <v>1.416</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4004</v>
+        <v>1.3631</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2004</v>
+        <v>-1.1684</v>
       </c>
       <c r="R2" t="n">
-        <v>2.6008</v>
+        <v>2.5316</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3915</v>
+        <v>0.3559</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9267000000000001</v>
+        <v>-0.8722000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3182</v>
+        <v>1.228</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9678</v>
+        <v>1.9847</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9192</v>
+        <v>3.0011</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.9512999999999999</v>
+        <v>-1.0165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8904</v>
+        <v>8.558900000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2305</v>
+        <v>15.6797</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6599</v>
+        <v>-7.120900000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>6.0804</v>
+        <v>4.714</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5767</v>
+        <v>-0.2932999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5037</v>
+        <v>5.007400000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1265</v>
+        <v>8.380700000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7995</v>
+        <v>1.5143</v>
       </c>
       <c r="L3" t="n">
-        <v>4.327</v>
+        <v>6.866199999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04600000000000004</v>
+        <v>-3.6666</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2228</v>
+        <v>-1.8076</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1768</v>
+        <v>-1.8589</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6002</v>
+        <v>3.5052</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-4.479</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6005</v>
+        <v>7.9842</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2985</v>
+        <v>-5.292</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8956999999999999</v>
+        <v>-2.9995</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5972999999999999</v>
+        <v>-2.2925</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5083</v>
+        <v>5.6315</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>14.7775</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5083</v>
+        <v>-9.146000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7124</v>
+        <v>6.0682</v>
       </c>
       <c r="E4" t="n">
-        <v>8.626200000000001</v>
+        <v>6.164</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9138</v>
+        <v>-0.09590000000000003</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2083</v>
+        <v>-0.8300999999999996</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06179999999999986</v>
+        <v>-1.5822</v>
       </c>
       <c r="I4" t="n">
-        <v>6.1465</v>
+        <v>0.7522000000000002</v>
       </c>
       <c r="J4" t="n">
-        <v>7.546</v>
+        <v>6.8583</v>
       </c>
       <c r="K4" t="n">
-        <v>1.305</v>
+        <v>1.3451</v>
       </c>
       <c r="L4" t="n">
-        <v>6.241</v>
+        <v>5.5136</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3377</v>
+        <v>-7.688499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2433</v>
+        <v>-2.9272</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.09449999999999992</v>
+        <v>-4.7613</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8005</v>
+        <v>4.6737</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4004</v>
+        <v>-8.373699999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2009</v>
+        <v>13.0473</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9039</v>
+        <v>-1.0911</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.218</v>
+        <v>-0.7132999999999998</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6859000000000001</v>
+        <v>-0.3779</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6074000000000002</v>
+        <v>3.3159</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6985</v>
+        <v>8.3926</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.0911</v>
+        <v>-5.0769</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>4.626300000000001</v>
+        <v>2.6968</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2325</v>
+        <v>-3.4496</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3938</v>
+        <v>6.146400000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.539</v>
+        <v>-1.0969</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9518</v>
+        <v>-2.296600000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5872</v>
+        <v>1.1995</v>
       </c>
       <c r="J5" t="n">
-        <v>6.071899999999999</v>
+        <v>4.3903</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0249</v>
+        <v>0.3292999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>4.047</v>
+        <v>4.0611</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5329</v>
+        <v>-5.487299999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0731</v>
+        <v>-2.6258</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4598</v>
+        <v>-2.8614</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2007</v>
+        <v>-2.3369</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.401</v>
+        <v>-12.0737</v>
       </c>
       <c r="R5" t="n">
-        <v>5.601599999999999</v>
+        <v>9.736800000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2328</v>
+        <v>7.9269</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1578</v>
+        <v>1.667</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07500000000000007</v>
+        <v>6.2601</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1195</v>
+        <v>-1.7963</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7194</v>
+        <v>2.5669</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5999</v>
+        <v>-4.3631</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.4204</v>
+        <v>0.9808000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2001</v>
+        <v>0.8135999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2203</v>
+        <v>0.167</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9291</v>
+        <v>2.4823</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5926</v>
+        <v>1.4495</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3364</v>
+        <v>1.0328</v>
       </c>
       <c r="J6" t="n">
-        <v>4.9244</v>
+        <v>3.3923</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7647</v>
+        <v>1.4703</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1597</v>
+        <v>1.922099999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9953</v>
+        <v>-0.9100000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.172</v>
+        <v>-0.02080000000000004</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1768000000000001</v>
+        <v>-0.8893</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.601</v>
+        <v>2.5315</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.2018</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6008</v>
+        <v>3.5052</v>
       </c>
       <c r="S6" t="n">
-        <v>3.0646</v>
+        <v>-1.7956</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5584</v>
+        <v>-1.6049</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5061</v>
+        <v>-0.1907000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0278</v>
+        <v>-2.2375</v>
       </c>
       <c r="W6" t="n">
-        <v>2.9191</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8913</v>
+        <v>-2.2375</v>
       </c>
     </row>
     <row r="7">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7777</v>
+        <v>-0.06119999999999992</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.1474</v>
+        <v>-0.7268000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3697</v>
+        <v>0.6657999999999998</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7318</v>
+        <v>0.9664000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6206</v>
+        <v>-0.2086999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1112</v>
+        <v>1.1753</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7088</v>
+        <v>3.937</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0346</v>
+        <v>1.1883</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6742</v>
+        <v>2.7487</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.023</v>
+        <v>-2.9706</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.586</v>
+        <v>-1.3972</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5629999999999999</v>
+        <v>-1.5734</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6002</v>
+        <v>3.1158</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2006</v>
+        <v>-3.1158</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6005</v>
+        <v>6.2316</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0456</v>
+        <v>-2.3986</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8379</v>
+        <v>-2.1588</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2077</v>
+        <v>-0.24</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5999</v>
+        <v>-1.7447</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.3552</v>
       </c>
     </row>
     <row r="8">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2837</v>
+        <v>-0.1890000000000005</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5483</v>
+        <v>2.853399999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2645</v>
+        <v>-3.0426</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.001300000000000079</v>
+        <v>2.3578</v>
       </c>
       <c r="H8" t="n">
-        <v>0.425</v>
+        <v>3.6326</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4262</v>
+        <v>-1.2748</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1344</v>
+        <v>4.8388</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1397</v>
+        <v>5.2112</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2741</v>
+        <v>-0.3724000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1332</v>
+        <v>-2.481</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7147</v>
+        <v>-1.5787</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8479000000000001</v>
+        <v>-0.9024</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0006</v>
+        <v>-4.8685</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6004</v>
+        <v>5.8422</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2509</v>
+        <v>-0.393</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2669</v>
+        <v>1.1546</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5178</v>
+        <v>-1.5476</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6315</v>
+        <v>-3.1276</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6802</v>
+        <v>1.7285</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9512999999999999</v>
+        <v>-4.856100000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3296</v>
+        <v>-1.9593</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2798</v>
+        <v>-1.865</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0498</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9278</v>
+        <v>-0.7229</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1027</v>
+        <v>0.214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.825</v>
+        <v>-0.9369</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5547</v>
+        <v>-0.644</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.087</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6417</v>
+        <v>-0.6645</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4823</v>
+        <v>-0.0789</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0156</v>
+        <v>0.1934</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4667</v>
+        <v>-0.2724</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4001</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2009</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>3.601</v>
+        <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9977</v>
+        <v>-0.4575</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.09310000000000018</v>
+        <v>-0.2473</v>
       </c>
       <c r="U9" t="n">
-        <v>2.0908</v>
+        <v>-0.2102</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.2592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2615</v>
+        <v>-4.855899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1929</v>
+        <v>-1.8392</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0685</v>
+        <v>-3.0168</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3406</v>
+        <v>-1.1294</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0445</v>
+        <v>3.6729</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3851</v>
+        <v>-4.802300000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>2.132499999999999</v>
+        <v>5.6738</v>
       </c>
       <c r="K10" t="n">
-        <v>2.881</v>
+        <v>6.3121</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7484999999999999</v>
+        <v>-0.6382000000000003</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.473</v>
+        <v>-6.8033</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8365</v>
+        <v>-2.6391</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.6366</v>
+        <v>-4.1642</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6001000000000001</v>
+        <v>-2.9211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.2012</v>
+        <v>-12.8526</v>
       </c>
       <c r="R10" t="n">
-        <v>3.601</v>
+        <v>9.9315</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5211</v>
+        <v>-2.5476</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6158999999999999</v>
+        <v>-0.4345000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1371</v>
+        <v>-2.113</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7997</v>
+        <v>1.7421</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2598</v>
+        <v>5.7743</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0595</v>
+        <v>-4.0322</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3535</v>
+        <v>-4.9937</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7938</v>
+        <v>-4.151999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5597</v>
+        <v>-0.8416999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4417</v>
+        <v>-1.1824</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1307</v>
+        <v>-2.1884</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.311</v>
+        <v>1.0061</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5686000000000002</v>
+        <v>0.3314999999999998</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.894</v>
+        <v>-1.2978</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3256</v>
+        <v>1.6293</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8732</v>
+        <v>-1.514</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2367000000000001</v>
+        <v>-0.8906000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.6366</v>
+        <v>-0.6234000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6004</v>
+        <v>-4.2842</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0009</v>
+        <v>-10.1264</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4004</v>
+        <v>5.8421</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8517999999999999</v>
+        <v>4.4171</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2244</v>
+        <v>3.51</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6274000000000001</v>
+        <v>0.9072</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4596</v>
+        <v>-3.9444</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.1327</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4596</v>
+        <v>-6.0771</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,148 +1342,226 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.2807</v>
+        <v>-9.588900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.001199999999999</v>
+        <v>-4.2592</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2795</v>
+        <v>-5.329800000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5182</v>
+        <v>-2.0794</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9515</v>
+        <v>-1.5477</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5667999999999997</v>
+        <v>-0.5316999999999996</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1986999999999997</v>
+        <v>2.3768</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0507</v>
+        <v>0.2849999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2494</v>
+        <v>2.092</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7169</v>
+        <v>-4.4562</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9008</v>
+        <v>-1.8326</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8161</v>
+        <v>-2.6234</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.6007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.201700000000001</v>
+        <v>-5.8422</v>
       </c>
       <c r="R12" t="n">
-        <v>3.601</v>
+        <v>3.505100000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.1617</v>
+        <v>-2.7821</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9982</v>
+        <v>-1.0734</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1635</v>
+        <v>-1.7089</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.3905</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>G. TSULAIA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TEKNEI BIZKAIA ZORNOTZA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-13.1387</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-15.1103</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.9714</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-7.244999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-5.0148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-2.2301</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-5.8993</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-4.5716</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.3278</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.3455</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.4430999999999999</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.9023999999999999</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-1.5579</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-8.178900000000001</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6.621</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-6.2191</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-3.7534</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-2.4657</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.8831</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.7217</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.8384</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>TEKNEI BIZKAIA ZORNOTZA</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.139800000000001</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5.889699999999996</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.2501</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14.8127</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.677299999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>12.1354</v>
-      </c>
-      <c r="J13" t="n">
-        <v>31.91459999999999</v>
-      </c>
-      <c r="K13" t="n">
-        <v>10.973</v>
-      </c>
-      <c r="L13" t="n">
-        <v>20.9418</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-17.1015</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-8.2956</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-8.8062</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-3.0006</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-34.0098</v>
-      </c>
-      <c r="R13" t="n">
-        <v>31.0089</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-3.8125</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-4.910600000000001</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.097999999999999</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-0.8598000000000003</v>
-      </c>
-      <c r="W13" t="n">
-        <v>12.8953</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-13.7549</v>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-5.696599999999995</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.143899999999997</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-6.841400000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.316100000000002</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.269599999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.586</v>
+      </c>
+      <c r="J14" t="n">
+        <v>39.711</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15.109</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.6026</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-36.395</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-16.3784</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-20.0165</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.9472</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-73.0266</v>
+      </c>
+      <c r="R14" t="n">
+        <v>74.97329999999999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-10.2767</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-7.525700000000001</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-2.751200000000001</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.6837</v>
+      </c>
+      <c r="W14" t="n">
+        <v>41.9853</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-42.669</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TEKNEI BIZKAIA ZORNOTZA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_TEKNEI BIZKAIA ZORNOTZA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7854</v>
+        <v>11.1825</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0353</v>
+        <v>17.1747</v>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>-5.9924</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0817</v>
+        <v>4.714</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8931</v>
+        <v>-0.2932999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>4.188499999999999</v>
+        <v>5.007400000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0748</v>
+        <v>8.380700000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3023</v>
+        <v>1.5143</v>
       </c>
       <c r="L2" t="n">
-        <v>2.7725</v>
+        <v>6.866199999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0069</v>
+        <v>-3.6666</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4091</v>
+        <v>-1.8076</v>
       </c>
       <c r="O2" t="n">
-        <v>1.416</v>
+        <v>-1.8589</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3631</v>
+        <v>3.5052</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1684</v>
+        <v>-4.479</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5316</v>
+        <v>7.9842</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3559</v>
+        <v>-2.6684</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8722000000000001</v>
+        <v>-1.5044</v>
       </c>
       <c r="U2" t="n">
-        <v>1.228</v>
+        <v>-1.1641</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9847</v>
+        <v>5.6315</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0011</v>
+        <v>14.7775</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0165</v>
+        <v>-9.146000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>8.558900000000001</v>
+        <v>11.1267</v>
       </c>
       <c r="E3" t="n">
-        <v>15.6797</v>
+        <v>7.6333</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.120900000000001</v>
+        <v>3.4934</v>
       </c>
       <c r="G3" t="n">
-        <v>4.714</v>
+        <v>7.0817</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2932999999999999</v>
+        <v>2.8931</v>
       </c>
       <c r="I3" t="n">
-        <v>5.007400000000001</v>
+        <v>4.188499999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>8.380700000000001</v>
+        <v>6.0748</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5143</v>
+        <v>3.3023</v>
       </c>
       <c r="L3" t="n">
-        <v>6.866199999999999</v>
+        <v>2.7725</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.6666</v>
+        <v>1.0069</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8076</v>
+        <v>-0.4091</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8589</v>
+        <v>1.416</v>
       </c>
       <c r="P3" t="n">
-        <v>3.5052</v>
+        <v>1.3631</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.479</v>
+        <v>-1.1684</v>
       </c>
       <c r="R3" t="n">
-        <v>7.9842</v>
+        <v>2.5316</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.292</v>
+        <v>0.6973</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.9995</v>
+        <v>-0.2741</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.2925</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>5.6315</v>
+        <v>1.9847</v>
       </c>
       <c r="W3" t="n">
-        <v>14.7775</v>
+        <v>3.0011</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.146000000000001</v>
+        <v>-1.0165</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0682</v>
+        <v>6.514900000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>6.164</v>
+        <v>6.1503</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09590000000000003</v>
+        <v>0.3647</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8300999999999996</v>
@@ -766,13 +766,13 @@
         <v>13.0473</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0911</v>
+        <v>-0.6445000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7132999999999998</v>
+        <v>-0.7272</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3779</v>
+        <v>0.08270000000000011</v>
       </c>
       <c r="V4" t="n">
         <v>3.3159</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6968</v>
+        <v>3.1453</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.4496</v>
+        <v>2.295</v>
       </c>
       <c r="F5" t="n">
-        <v>6.146400000000001</v>
+        <v>0.8502</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0969</v>
+        <v>2.4823</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.296600000000001</v>
+        <v>1.4495</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1995</v>
+        <v>1.0328</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3903</v>
+        <v>3.3923</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3292999999999999</v>
+        <v>1.4703</v>
       </c>
       <c r="L5" t="n">
-        <v>4.0611</v>
+        <v>1.922099999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.487299999999999</v>
+        <v>-0.9100000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.6258</v>
+        <v>-0.02080000000000004</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.8614</v>
+        <v>-0.8893</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.3369</v>
+        <v>2.5315</v>
       </c>
       <c r="Q5" t="n">
-        <v>-12.0737</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>9.736800000000001</v>
+        <v>3.5052</v>
       </c>
       <c r="S5" t="n">
-        <v>7.9269</v>
+        <v>0.369</v>
       </c>
       <c r="T5" t="n">
-        <v>1.667</v>
+        <v>-0.1236</v>
       </c>
       <c r="U5" t="n">
-        <v>6.2601</v>
+        <v>0.4926</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7963</v>
+        <v>-2.2375</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5669</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.3631</v>
+        <v>-2.2375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9808000000000001</v>
+        <v>2.3228</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8135999999999999</v>
+        <v>0.9677</v>
       </c>
       <c r="F6" t="n">
-        <v>0.167</v>
+        <v>1.3551</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4823</v>
+        <v>0.9664000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4495</v>
+        <v>-0.2086999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0328</v>
+        <v>1.1753</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3923</v>
+        <v>3.937</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4703</v>
+        <v>1.1883</v>
       </c>
       <c r="L6" t="n">
-        <v>1.922099999999999</v>
+        <v>2.7487</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9100000000000001</v>
+        <v>-2.9706</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02080000000000004</v>
+        <v>-1.3972</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8893</v>
+        <v>-1.5734</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5315</v>
+        <v>3.1158</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9737</v>
+        <v>-3.1158</v>
       </c>
       <c r="R6" t="n">
-        <v>3.5052</v>
+        <v>6.2316</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7956</v>
+        <v>-0.01490000000000006</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6049</v>
+        <v>-0.4641</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1907000000000001</v>
+        <v>0.4494</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.2375</v>
+        <v>-1.7447</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2375</v>
+        <v>-2.3552</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.06119999999999992</v>
+        <v>-0.05139999999999967</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7268000000000001</v>
+        <v>1.980400000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6657999999999998</v>
+        <v>-2.0318</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9664000000000001</v>
+        <v>2.3578</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2086999999999999</v>
+        <v>3.6326</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1753</v>
+        <v>-1.2748</v>
       </c>
       <c r="J7" t="n">
-        <v>3.937</v>
+        <v>4.8388</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1883</v>
+        <v>5.2112</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7487</v>
+        <v>-0.3724000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9706</v>
+        <v>-2.481</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3972</v>
+        <v>-1.5787</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5734</v>
+        <v>-0.9024</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1158</v>
+        <v>0.9737</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1158</v>
+        <v>-4.8685</v>
       </c>
       <c r="R7" t="n">
-        <v>6.2316</v>
+        <v>5.8422</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.3986</v>
+        <v>-0.2552</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.1588</v>
+        <v>0.2815</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.24</v>
+        <v>-0.5367</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7447</v>
+        <v>-3.1276</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6105</v>
+        <v>1.7285</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3552</v>
+        <v>-4.856100000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1890000000000005</v>
+        <v>-1.8759</v>
       </c>
       <c r="E8" t="n">
-        <v>2.853399999999999</v>
+        <v>-1.865</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0426</v>
+        <v>-0.0109</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3578</v>
+        <v>-0.7229</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6326</v>
+        <v>0.214</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2748</v>
+        <v>-0.9369</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8388</v>
+        <v>-0.644</v>
       </c>
       <c r="K8" t="n">
-        <v>5.2112</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3724000000000001</v>
+        <v>-0.6645</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.481</v>
+        <v>-0.0789</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5787</v>
+        <v>0.1934</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9024</v>
+        <v>-0.2724</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9737</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.8685</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>5.8422</v>
+        <v>0.1947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.393</v>
+        <v>-0.374</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1546</v>
+        <v>-0.2473</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.5476</v>
+        <v>-0.1267</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1276</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7285</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.856100000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9593</v>
+        <v>-3.0526</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.865</v>
+        <v>-5.157900000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09429999999999999</v>
+        <v>2.105300000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7229</v>
+        <v>-1.0969</v>
       </c>
       <c r="H9" t="n">
-        <v>0.214</v>
+        <v>-2.296600000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9369</v>
+        <v>1.1995</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.644</v>
+        <v>4.3903</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0205</v>
+        <v>0.3292999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6645</v>
+        <v>4.0611</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0789</v>
+        <v>-5.487299999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1934</v>
+        <v>-2.6258</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2724</v>
+        <v>-2.8614</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7789</v>
+        <v>-2.3369</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9737</v>
+        <v>-12.0737</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1947</v>
+        <v>9.736800000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4575</v>
+        <v>2.1776</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2473</v>
+        <v>-0.0414000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2102</v>
+        <v>2.219</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.7963</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.5669</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-4.3631</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.855899999999999</v>
+        <v>-4.411200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8392</v>
+        <v>-2.6745</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0168</v>
+        <v>-1.7368</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1294</v>
@@ -1234,13 +1234,13 @@
         <v>9.9315</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.5476</v>
+        <v>-2.1029</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4345000000000001</v>
+        <v>-1.2698</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.113</v>
+        <v>-0.8330000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>1.7421</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9937</v>
+        <v>-8.315999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.151999999999999</v>
+        <v>-3.9601</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8416999999999999</v>
+        <v>-4.356</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1824</v>
+        <v>-2.0794</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1884</v>
+        <v>-1.5477</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0061</v>
+        <v>-0.5316999999999996</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3314999999999998</v>
+        <v>2.3768</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2978</v>
+        <v>0.2849999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6293</v>
+        <v>2.092</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.514</v>
+        <v>-4.4562</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8906000000000001</v>
+        <v>-1.8326</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6234000000000001</v>
+        <v>-2.6234</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.2842</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.1264</v>
+        <v>-5.8422</v>
       </c>
       <c r="R11" t="n">
-        <v>5.8421</v>
+        <v>3.505100000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4171</v>
+        <v>-1.5091</v>
       </c>
       <c r="T11" t="n">
-        <v>3.51</v>
+        <v>-0.7743</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9072</v>
+        <v>-0.7349</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.9444</v>
+        <v>-2.3905</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1327</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.0771</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.588900000000001</v>
+        <v>-8.645800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2592</v>
+        <v>-6.9569</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.329800000000001</v>
+        <v>-1.689</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0794</v>
+        <v>-1.1824</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5477</v>
+        <v>-2.1884</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5316999999999996</v>
+        <v>1.0061</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3768</v>
+        <v>0.3314999999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2849999999999999</v>
+        <v>-1.2978</v>
       </c>
       <c r="L12" t="n">
-        <v>2.092</v>
+        <v>1.6293</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.4562</v>
+        <v>-1.514</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8326</v>
+        <v>-0.8906000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.6234</v>
+        <v>-0.6234000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3368</v>
+        <v>-4.2842</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8422</v>
+        <v>-10.1264</v>
       </c>
       <c r="R12" t="n">
-        <v>3.505100000000001</v>
+        <v>5.8421</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7821</v>
+        <v>0.7650999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0734</v>
+        <v>0.7052</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7089</v>
+        <v>0.05999999999999995</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3905</v>
+        <v>-3.9444</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2795</v>
+        <v>2.1327</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.67</v>
+        <v>-6.0771</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.1387</v>
+        <v>-10.7154</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.1103</v>
+        <v>-13.5154</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9714</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
         <v>-7.244999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>6.621</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.2191</v>
+        <v>-3.7957</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7534</v>
+        <v>-2.1587</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.4657</v>
+        <v>-1.6371</v>
       </c>
       <c r="V13" t="n">
         <v>1.8831</v>
@@ -1501,19 +1501,19 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.696599999999995</v>
+        <v>-2.776100000000005</v>
       </c>
       <c r="E14" t="n">
-        <v>1.143899999999997</v>
+        <v>2.071599999999995</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.841400000000001</v>
+        <v>-4.848199999999999</v>
       </c>
       <c r="G14" t="n">
         <v>3.316100000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.269599999999999</v>
+        <v>-1.2696</v>
       </c>
       <c r="I14" t="n">
         <v>4.586</v>
@@ -1540,19 +1540,19 @@
         <v>1.9472</v>
       </c>
       <c r="Q14" t="n">
-        <v>-73.0266</v>
+        <v>-73.02659999999999</v>
       </c>
       <c r="R14" t="n">
         <v>74.97329999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.2767</v>
+        <v>-7.355700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.525700000000001</v>
+        <v>-6.5982</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.751200000000001</v>
+        <v>-0.7575000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6837</v>
